--- a/data/trans_orig/LAWTONBRODY-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONBRODY-Estudios-trans_orig.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,78; 7,18</t>
+          <t>6,78; 7,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,29; 6,82</t>
+          <t>6,27; 6,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,64; 7,07</t>
+          <t>6,65; 7,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,52; 6,89</t>
+          <t>6,55; 6,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,91; 6,36</t>
+          <t>5,91; 6,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,18; 6,65</t>
+          <t>6,19; 6,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,68; 6,96</t>
+          <t>6,68; 6,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,13; 6,48</t>
+          <t>6,14; 6,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,45; 6,77</t>
+          <t>6,43; 6,78</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,0; 7,68</t>
+          <t>6,96; 7,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,71; 7,52</t>
+          <t>6,76; 7,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,32; 7,72</t>
+          <t>7,34; 7,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,32; 7,48</t>
+          <t>6,27; 7,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,34; 7,45</t>
+          <t>6,36; 7,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,68; 7,31</t>
+          <t>6,65; 7,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,9; 7,52</t>
+          <t>6,88; 7,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,76; 7,4</t>
+          <t>6,79; 7,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,07; 7,46</t>
+          <t>7,06; 7,47</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,86; 7,72</t>
+          <t>6,85; 7,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,72; 8,0</t>
+          <t>6,67; 8,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,79</t>
+          <t>6,8; 7,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 7,51</t>
+          <t>6,43; 7,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,12; 7,73</t>
+          <t>5,4; 7,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,65; 7,76</t>
+          <t>5,37; 7,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,86; 7,55</t>
+          <t>6,89; 7,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,44; 7,75</t>
+          <t>6,52; 7,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,77; 7,64</t>
+          <t>6,76; 7,67</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,5; 6,96</t>
+          <t>6,5; 6,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1022,32 +1022,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,58; 6,93</t>
+          <t>6,58; 6,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,05; 6,44</t>
+          <t>6,04; 6,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,4; 6,77</t>
+          <t>6,41; 6,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,79; 7,02</t>
+          <t>6,78; 7,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,31; 6,62</t>
+          <t>6,3; 6,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 6,95</t>
+          <t>6,7; 6,94</t>
         </is>
       </c>
     </row>
